--- a/results/data/semih_async_curriculum_dqn_experiment_results.xlsx
+++ b/results/data/semih_async_curriculum_dqn_experiment_results.xlsx
@@ -750,190 +750,190 @@
         <v>1</v>
       </c>
       <c r="B2" t="n">
-        <v>195.9</v>
+        <v>286.2</v>
       </c>
       <c r="C2" t="n">
-        <v>16.51938255504727</v>
+        <v>30.36050065463348</v>
       </c>
       <c r="D2" t="n">
-        <v>197.2</v>
+        <v>278.7</v>
       </c>
       <c r="E2" t="n">
-        <v>33.31606219228198</v>
+        <v>29.12747843531946</v>
       </c>
       <c r="F2" t="n">
-        <v>185.2</v>
+        <v>295.7</v>
       </c>
       <c r="G2" t="n">
-        <v>25.16267076444788</v>
+        <v>33.27476521329639</v>
       </c>
       <c r="H2" t="n">
-        <v>191.8</v>
+        <v>282.9</v>
       </c>
       <c r="I2" t="n">
-        <v>28.37886537548674</v>
+        <v>29.3545567161216</v>
       </c>
       <c r="J2" t="n">
-        <v>181.9</v>
+        <v>287.8</v>
       </c>
       <c r="K2" t="n">
-        <v>22.39843744550052</v>
+        <v>29.14378149794566</v>
       </c>
       <c r="L2" t="n">
-        <v>190.2</v>
+        <v>293.9</v>
       </c>
       <c r="M2" t="n">
-        <v>28.5545092761196</v>
+        <v>27.6530287672074</v>
       </c>
       <c r="N2" t="n">
-        <v>196.1</v>
+        <v>315.2</v>
       </c>
       <c r="O2" t="n">
-        <v>30.63151971417677</v>
+        <v>35.68417015989022</v>
       </c>
       <c r="P2" t="n">
-        <v>220.3</v>
+        <v>311.4</v>
       </c>
       <c r="Q2" t="n">
-        <v>36.98932278374396</v>
+        <v>33.14573879098187</v>
       </c>
       <c r="R2" t="n">
-        <v>177.2</v>
+        <v>334</v>
       </c>
       <c r="S2" t="n">
-        <v>27.11383410733347</v>
+        <v>14.4291371883422</v>
       </c>
       <c r="T2" t="n">
-        <v>192.5</v>
+        <v>328.2</v>
       </c>
       <c r="U2" t="n">
-        <v>50.1422975141746</v>
+        <v>43.43224608513817</v>
       </c>
       <c r="V2" t="n">
-        <v>192.5</v>
+        <v>353.5</v>
       </c>
       <c r="W2" t="n">
-        <v>70.69264459616714</v>
+        <v>94.53491418518345</v>
       </c>
       <c r="X2" t="n">
-        <v>194.9</v>
+        <v>343.3</v>
       </c>
       <c r="Y2" t="n">
-        <v>70.80176551471016</v>
+        <v>54.48311665094059</v>
       </c>
       <c r="Z2" t="n">
-        <v>200.3</v>
+        <v>341.4</v>
       </c>
       <c r="AA2" t="n">
-        <v>40.0875292329173</v>
+        <v>59.67109853186884</v>
       </c>
       <c r="AB2" t="n">
-        <v>189.6</v>
+        <v>326.9</v>
       </c>
       <c r="AC2" t="n">
-        <v>48.70769959667568</v>
+        <v>58.53793641733538</v>
       </c>
       <c r="AD2" t="n">
-        <v>221</v>
+        <v>323.9</v>
       </c>
       <c r="AE2" t="n">
-        <v>39.33192087859427</v>
+        <v>29.14258053090014</v>
       </c>
       <c r="AF2" t="n">
-        <v>219.3</v>
+        <v>333.9</v>
       </c>
       <c r="AG2" t="n">
-        <v>27.7274232484737</v>
+        <v>65.00992231959671</v>
       </c>
       <c r="AH2" t="n">
-        <v>205.4</v>
+        <v>323.1</v>
       </c>
       <c r="AI2" t="n">
-        <v>35.77205613324457</v>
+        <v>35.65515390515094</v>
       </c>
       <c r="AJ2" t="n">
-        <v>206.6</v>
+        <v>356.8</v>
       </c>
       <c r="AK2" t="n">
-        <v>23.47850080392698</v>
+        <v>61.37556517051391</v>
       </c>
       <c r="AL2" t="n">
-        <v>204.6</v>
+        <v>344.3</v>
       </c>
       <c r="AM2" t="n">
-        <v>51.65500943761408</v>
+        <v>84.38015169457803</v>
       </c>
       <c r="AN2" t="n">
-        <v>207.8</v>
+        <v>327.4</v>
       </c>
       <c r="AO2" t="n">
-        <v>32.40000000000001</v>
+        <v>31.81257612957492</v>
       </c>
       <c r="AP2" t="n">
-        <v>231.3</v>
+        <v>318.6</v>
       </c>
       <c r="AQ2" t="n">
-        <v>53.63403769995319</v>
+        <v>36.78912882904405</v>
       </c>
       <c r="AR2" t="n">
-        <v>220.7</v>
+        <v>335.2</v>
       </c>
       <c r="AS2" t="n">
-        <v>49.79969879426983</v>
+        <v>34.75571895386427</v>
       </c>
       <c r="AT2" t="n">
-        <v>217.9</v>
+        <v>339.1</v>
       </c>
       <c r="AU2" t="n">
-        <v>34.34079207007317</v>
+        <v>62.64415375755346</v>
       </c>
       <c r="AV2" t="n">
-        <v>242.9</v>
+        <v>311.9</v>
       </c>
       <c r="AW2" t="n">
-        <v>66.79139166090194</v>
+        <v>20.73861133248801</v>
       </c>
       <c r="AX2" t="n">
-        <v>214.2</v>
+        <v>326.1</v>
       </c>
       <c r="AY2" t="n">
-        <v>50.20717080258556</v>
+        <v>35.48083989986708</v>
       </c>
       <c r="AZ2" t="n">
-        <v>251.2</v>
+        <v>328</v>
       </c>
       <c r="BA2" t="n">
-        <v>67.34508148335705</v>
+        <v>31.34964114627152</v>
       </c>
       <c r="BB2" t="n">
-        <v>292.7</v>
+        <v>324.3</v>
       </c>
       <c r="BC2" t="n">
-        <v>92.44463207780105</v>
+        <v>20.23882407651196</v>
       </c>
       <c r="BD2" t="n">
-        <v>254.8</v>
+        <v>354</v>
       </c>
       <c r="BE2" t="n">
-        <v>76.64567828651528</v>
+        <v>50.31699514080705</v>
       </c>
       <c r="BF2" t="n">
-        <v>268.8</v>
+        <v>357.9</v>
       </c>
       <c r="BG2" t="n">
-        <v>23.26284591360223</v>
+        <v>80.07802445115638</v>
       </c>
       <c r="BH2" t="n">
-        <v>248.4</v>
+        <v>320</v>
       </c>
       <c r="BI2" t="n">
-        <v>93.56195808126292</v>
+        <v>14.52583904633395</v>
       </c>
       <c r="BJ2" t="n">
-        <v>6413.199999999999</v>
+        <v>9703.599999999999</v>
       </c>
       <c r="BK2" t="n">
-        <v>213.7733333333333</v>
+        <v>323.4533333333333</v>
       </c>
     </row>
     <row r="3">
@@ -941,190 +941,190 @@
         <v>2</v>
       </c>
       <c r="B3" t="n">
-        <v>182.7</v>
+        <v>274.4</v>
       </c>
       <c r="C3" t="n">
-        <v>30.19950330717378</v>
+        <v>29.61823762481488</v>
       </c>
       <c r="D3" t="n">
-        <v>180.4</v>
+        <v>275</v>
       </c>
       <c r="E3" t="n">
-        <v>23.95078286820704</v>
+        <v>24.94393713911258</v>
       </c>
       <c r="F3" t="n">
-        <v>202.3</v>
+        <v>302.3</v>
       </c>
       <c r="G3" t="n">
-        <v>11.15392307665783</v>
+        <v>31.77750776886067</v>
       </c>
       <c r="H3" t="n">
-        <v>207.6</v>
+        <v>269.2</v>
       </c>
       <c r="I3" t="n">
-        <v>19.64281038955475</v>
+        <v>17.91535654124695</v>
       </c>
       <c r="J3" t="n">
-        <v>186.3</v>
+        <v>297.2</v>
       </c>
       <c r="K3" t="n">
-        <v>46.88507225119739</v>
+        <v>30.86357075906804</v>
       </c>
       <c r="L3" t="n">
-        <v>220.7</v>
+        <v>295.6</v>
       </c>
       <c r="M3" t="n">
-        <v>38.8331044342324</v>
+        <v>31.06509295012651</v>
       </c>
       <c r="N3" t="n">
-        <v>200.9</v>
+        <v>329.7</v>
       </c>
       <c r="O3" t="n">
-        <v>41.40881548656035</v>
+        <v>59.76127508679846</v>
       </c>
       <c r="P3" t="n">
-        <v>210.7</v>
+        <v>303.8</v>
       </c>
       <c r="Q3" t="n">
-        <v>65.4828985308378</v>
+        <v>36.83965254993592</v>
       </c>
       <c r="R3" t="n">
-        <v>205.2</v>
+        <v>319.8</v>
       </c>
       <c r="S3" t="n">
-        <v>50.05956452067876</v>
+        <v>32.16768564879979</v>
       </c>
       <c r="T3" t="n">
-        <v>205.2</v>
+        <v>313</v>
       </c>
       <c r="U3" t="n">
-        <v>39.6050501830259</v>
+        <v>34.35403906384226</v>
       </c>
       <c r="V3" t="n">
-        <v>232.6</v>
+        <v>336.2</v>
       </c>
       <c r="W3" t="n">
-        <v>70.54672210670033</v>
+        <v>25.65852684781416</v>
       </c>
       <c r="X3" t="n">
-        <v>204.3</v>
+        <v>316</v>
       </c>
       <c r="Y3" t="n">
-        <v>24.99619971115609</v>
+        <v>28.2948758611873</v>
       </c>
       <c r="Z3" t="n">
-        <v>229.6</v>
+        <v>326.5</v>
       </c>
       <c r="AA3" t="n">
-        <v>71.78467803090015</v>
+        <v>12.06855418018248</v>
       </c>
       <c r="AB3" t="n">
-        <v>202.4</v>
+        <v>400.4</v>
       </c>
       <c r="AC3" t="n">
-        <v>44.98044019348855</v>
+        <v>222.0910624045911</v>
       </c>
       <c r="AD3" t="n">
-        <v>210.2</v>
+        <v>356.9</v>
       </c>
       <c r="AE3" t="n">
-        <v>66.08751773217087</v>
+        <v>71.76273406162839</v>
       </c>
       <c r="AF3" t="n">
-        <v>219.6</v>
+        <v>317</v>
       </c>
       <c r="AG3" t="n">
-        <v>29.78657415682441</v>
+        <v>30.25557799811466</v>
       </c>
       <c r="AH3" t="n">
-        <v>212</v>
+        <v>340</v>
       </c>
       <c r="AI3" t="n">
-        <v>49.51565409039853</v>
+        <v>57.81003373117854</v>
       </c>
       <c r="AJ3" t="n">
-        <v>194.7</v>
+        <v>326</v>
       </c>
       <c r="AK3" t="n">
-        <v>35.83308527045919</v>
+        <v>29</v>
       </c>
       <c r="AL3" t="n">
-        <v>257.8</v>
+        <v>320.6</v>
       </c>
       <c r="AM3" t="n">
-        <v>108.9346593146552</v>
+        <v>26.4733828590152</v>
       </c>
       <c r="AN3" t="n">
-        <v>211.9</v>
+        <v>341.5</v>
       </c>
       <c r="AO3" t="n">
-        <v>73.15387891287789</v>
+        <v>63.49685031558652</v>
       </c>
       <c r="AP3" t="n">
-        <v>217.9</v>
+        <v>327.7</v>
       </c>
       <c r="AQ3" t="n">
-        <v>16.04026184324931</v>
+        <v>44.44108459522562</v>
       </c>
       <c r="AR3" t="n">
-        <v>219.8</v>
+        <v>325.8</v>
       </c>
       <c r="AS3" t="n">
-        <v>41.4724004610295</v>
+        <v>57.78719581360563</v>
       </c>
       <c r="AT3" t="n">
-        <v>205.7</v>
+        <v>333.9</v>
       </c>
       <c r="AU3" t="n">
-        <v>33.74033194857454</v>
+        <v>19.82649742138031</v>
       </c>
       <c r="AV3" t="n">
-        <v>206</v>
+        <v>312.1</v>
       </c>
       <c r="AW3" t="n">
-        <v>21.73476477903545</v>
+        <v>24.37806390999909</v>
       </c>
       <c r="AX3" t="n">
-        <v>224.7</v>
+        <v>320.3</v>
       </c>
       <c r="AY3" t="n">
-        <v>52.19396516839854</v>
+        <v>17.57299063904605</v>
       </c>
       <c r="AZ3" t="n">
-        <v>191.8</v>
+        <v>337.5</v>
       </c>
       <c r="BA3" t="n">
-        <v>42.31028243819698</v>
+        <v>47.8419272187064</v>
       </c>
       <c r="BB3" t="n">
-        <v>233.1</v>
+        <v>334.2</v>
       </c>
       <c r="BC3" t="n">
-        <v>44.35865191819968</v>
+        <v>55.38736317970011</v>
       </c>
       <c r="BD3" t="n">
-        <v>204.6</v>
+        <v>330</v>
       </c>
       <c r="BE3" t="n">
-        <v>50.29751484914538</v>
+        <v>15.95619002143055</v>
       </c>
       <c r="BF3" t="n">
-        <v>261</v>
+        <v>343.4</v>
       </c>
       <c r="BG3" t="n">
-        <v>88.87519338938172</v>
+        <v>73.89343678568483</v>
       </c>
       <c r="BH3" t="n">
-        <v>264</v>
+        <v>347.3</v>
       </c>
       <c r="BI3" t="n">
-        <v>82.26177727231524</v>
+        <v>50.37271086610289</v>
       </c>
       <c r="BJ3" t="n">
-        <v>6405.700000000001</v>
+        <v>9673.300000000001</v>
       </c>
       <c r="BK3" t="n">
-        <v>213.5233333333334</v>
+        <v>322.4433333333334</v>
       </c>
     </row>
     <row r="4">
@@ -1132,190 +1132,190 @@
         <v>3</v>
       </c>
       <c r="B4" t="n">
-        <v>180.9</v>
+        <v>294.2</v>
       </c>
       <c r="C4" t="n">
-        <v>24.43951718017359</v>
+        <v>37.37592808212258</v>
       </c>
       <c r="D4" t="n">
-        <v>189.1</v>
+        <v>291.7</v>
       </c>
       <c r="E4" t="n">
-        <v>34.70576321016439</v>
+        <v>38.14459332592235</v>
       </c>
       <c r="F4" t="n">
-        <v>196.7</v>
+        <v>290.7</v>
       </c>
       <c r="G4" t="n">
-        <v>8.34326075344646</v>
+        <v>35.5078864479428</v>
       </c>
       <c r="H4" t="n">
-        <v>195.8</v>
+        <v>276</v>
       </c>
       <c r="I4" t="n">
-        <v>31.68848371254138</v>
+        <v>23.47338918861101</v>
       </c>
       <c r="J4" t="n">
-        <v>198.6</v>
+        <v>289.3</v>
       </c>
       <c r="K4" t="n">
-        <v>27.60507199773259</v>
+        <v>30.96142761566398</v>
       </c>
       <c r="L4" t="n">
-        <v>203.4</v>
+        <v>284.6</v>
       </c>
       <c r="M4" t="n">
-        <v>63.04157358442126</v>
+        <v>31.08440123277268</v>
       </c>
       <c r="N4" t="n">
-        <v>197.6</v>
+        <v>309.9</v>
       </c>
       <c r="O4" t="n">
-        <v>37.68076432345819</v>
+        <v>36.42650134174294</v>
       </c>
       <c r="P4" t="n">
-        <v>200.7</v>
+        <v>321.7</v>
       </c>
       <c r="Q4" t="n">
-        <v>30.25243791829016</v>
+        <v>62.42443431862238</v>
       </c>
       <c r="R4" t="n">
-        <v>221</v>
+        <v>305.9</v>
       </c>
       <c r="S4" t="n">
-        <v>46.87643331141993</v>
+        <v>33.47670832086094</v>
       </c>
       <c r="T4" t="n">
-        <v>214.9</v>
+        <v>318.9</v>
       </c>
       <c r="U4" t="n">
-        <v>28.59527933068673</v>
+        <v>30.0747402316296</v>
       </c>
       <c r="V4" t="n">
-        <v>233.8</v>
+        <v>322.5</v>
       </c>
       <c r="W4" t="n">
-        <v>63.76958522681483</v>
+        <v>32.35815198678689</v>
       </c>
       <c r="X4" t="n">
-        <v>215.9</v>
+        <v>322.2</v>
       </c>
       <c r="Y4" t="n">
-        <v>22.42966785309136</v>
+        <v>32.67659713005624</v>
       </c>
       <c r="Z4" t="n">
-        <v>191</v>
+        <v>319.5</v>
       </c>
       <c r="AA4" t="n">
-        <v>33.55592347112503</v>
+        <v>21.86435455255883</v>
       </c>
       <c r="AB4" t="n">
-        <v>223.9</v>
+        <v>339.5</v>
       </c>
       <c r="AC4" t="n">
-        <v>53.54147924740219</v>
+        <v>85.07555465584694</v>
       </c>
       <c r="AD4" t="n">
-        <v>193</v>
+        <v>331.4</v>
       </c>
       <c r="AE4" t="n">
-        <v>40.57092555020159</v>
+        <v>56.6572148980163</v>
       </c>
       <c r="AF4" t="n">
-        <v>209.5</v>
+        <v>315.8</v>
       </c>
       <c r="AG4" t="n">
-        <v>35.76380852202405</v>
+        <v>38.31135601880988</v>
       </c>
       <c r="AH4" t="n">
-        <v>190.3</v>
+        <v>314.1</v>
       </c>
       <c r="AI4" t="n">
-        <v>45.55008232703867</v>
+        <v>31.51650361318654</v>
       </c>
       <c r="AJ4" t="n">
-        <v>206.2</v>
+        <v>316.8</v>
       </c>
       <c r="AK4" t="n">
-        <v>41.62162899262834</v>
+        <v>23.40427311411316</v>
       </c>
       <c r="AL4" t="n">
-        <v>227.3</v>
+        <v>332.5</v>
       </c>
       <c r="AM4" t="n">
-        <v>44.42758152319345</v>
+        <v>36.7239703735857</v>
       </c>
       <c r="AN4" t="n">
-        <v>233.3</v>
+        <v>295.7</v>
       </c>
       <c r="AO4" t="n">
-        <v>48.98173128830789</v>
+        <v>32.87871651996166</v>
       </c>
       <c r="AP4" t="n">
-        <v>203.6</v>
+        <v>311.2</v>
       </c>
       <c r="AQ4" t="n">
-        <v>36.95456670020635</v>
+        <v>16.06113321033108</v>
       </c>
       <c r="AR4" t="n">
-        <v>256.3</v>
+        <v>337.9</v>
       </c>
       <c r="AS4" t="n">
-        <v>101.4130662192994</v>
+        <v>56.25379987165311</v>
       </c>
       <c r="AT4" t="n">
-        <v>234</v>
+        <v>326.8</v>
       </c>
       <c r="AU4" t="n">
-        <v>31.85278637733283</v>
+        <v>44.93951490614914</v>
       </c>
       <c r="AV4" t="n">
-        <v>225</v>
+        <v>321.9</v>
       </c>
       <c r="AW4" t="n">
-        <v>58.6208154156866</v>
+        <v>17.59232787325202</v>
       </c>
       <c r="AX4" t="n">
-        <v>206.7</v>
+        <v>324.3</v>
       </c>
       <c r="AY4" t="n">
-        <v>42.42652472215936</v>
+        <v>49.27281197577423</v>
       </c>
       <c r="AZ4" t="n">
-        <v>236.9</v>
+        <v>340.8</v>
       </c>
       <c r="BA4" t="n">
-        <v>67.80036873056075</v>
+        <v>40.44700236111448</v>
       </c>
       <c r="BB4" t="n">
-        <v>241.5</v>
+        <v>318</v>
       </c>
       <c r="BC4" t="n">
-        <v>58.73712624907692</v>
+        <v>48.88762624632127</v>
       </c>
       <c r="BD4" t="n">
-        <v>257.2</v>
+        <v>332.3</v>
       </c>
       <c r="BE4" t="n">
-        <v>43.4</v>
+        <v>73.44800882256781</v>
       </c>
       <c r="BF4" t="n">
-        <v>275.5</v>
+        <v>344.9</v>
       </c>
       <c r="BG4" t="n">
-        <v>86.63746302841514</v>
+        <v>48.2254082408848</v>
       </c>
       <c r="BH4" t="n">
-        <v>254.1</v>
+        <v>325.3</v>
       </c>
       <c r="BI4" t="n">
-        <v>93.25604538044705</v>
+        <v>53.52765640302217</v>
       </c>
       <c r="BJ4" t="n">
-        <v>6513.700000000001</v>
+        <v>9476.299999999997</v>
       </c>
       <c r="BK4" t="n">
-        <v>217.1233333333334</v>
+        <v>315.8766666666666</v>
       </c>
     </row>
     <row r="5">
@@ -1323,190 +1323,190 @@
         <v>4</v>
       </c>
       <c r="B5" t="n">
-        <v>191.5</v>
+        <v>301.7</v>
       </c>
       <c r="C5" t="n">
-        <v>16.03277892319357</v>
+        <v>33.00318166480317</v>
       </c>
       <c r="D5" t="n">
-        <v>192.9</v>
+        <v>309</v>
       </c>
       <c r="E5" t="n">
-        <v>17.04963342714441</v>
+        <v>32.51768749465435</v>
       </c>
       <c r="F5" t="n">
-        <v>205.7</v>
+        <v>311.8</v>
       </c>
       <c r="G5" t="n">
-        <v>39.46150022490275</v>
+        <v>26.84324868565651</v>
       </c>
       <c r="H5" t="n">
-        <v>189.5</v>
+        <v>282</v>
       </c>
       <c r="I5" t="n">
-        <v>50.30755410472666</v>
+        <v>27.69115382211438</v>
       </c>
       <c r="J5" t="n">
-        <v>190.8</v>
+        <v>306.2</v>
       </c>
       <c r="K5" t="n">
-        <v>40.8724846320847</v>
+        <v>36.54805056360735</v>
       </c>
       <c r="L5" t="n">
-        <v>224.2</v>
+        <v>303.3</v>
       </c>
       <c r="M5" t="n">
-        <v>44.88830582679636</v>
+        <v>33.24169069105842</v>
       </c>
       <c r="N5" t="n">
-        <v>203.5</v>
+        <v>300.4</v>
       </c>
       <c r="O5" t="n">
-        <v>39.02371074103538</v>
+        <v>27.64489102890442</v>
       </c>
       <c r="P5" t="n">
-        <v>203.3</v>
+        <v>343.2</v>
       </c>
       <c r="Q5" t="n">
-        <v>36.1359931370372</v>
+        <v>28.67681990737467</v>
       </c>
       <c r="R5" t="n">
-        <v>193.5</v>
+        <v>308.2</v>
       </c>
       <c r="S5" t="n">
-        <v>43.22094399709474</v>
+        <v>30.3572067226219</v>
       </c>
       <c r="T5" t="n">
-        <v>202.8</v>
+        <v>311.5</v>
       </c>
       <c r="U5" t="n">
-        <v>31.2499599999744</v>
+        <v>23.6146141192271</v>
       </c>
       <c r="V5" t="n">
-        <v>210</v>
+        <v>335.6</v>
       </c>
       <c r="W5" t="n">
-        <v>24.71841418861655</v>
+        <v>52.01192171031561</v>
       </c>
       <c r="X5" t="n">
-        <v>196.1</v>
+        <v>355.9</v>
       </c>
       <c r="Y5" t="n">
-        <v>39.00371777151506</v>
+        <v>64.65980204114454</v>
       </c>
       <c r="Z5" t="n">
-        <v>192.1</v>
+        <v>367.4</v>
       </c>
       <c r="AA5" t="n">
-        <v>41.72876705583332</v>
+        <v>66.26190459079787</v>
       </c>
       <c r="AB5" t="n">
-        <v>209.4</v>
+        <v>332.6</v>
       </c>
       <c r="AC5" t="n">
-        <v>29.68905522242161</v>
+        <v>58.21546186366643</v>
       </c>
       <c r="AD5" t="n">
-        <v>197.8</v>
+        <v>315.2</v>
       </c>
       <c r="AE5" t="n">
-        <v>38.12820478333592</v>
+        <v>36.33400610997911</v>
       </c>
       <c r="AF5" t="n">
-        <v>212.8</v>
+        <v>333.1</v>
       </c>
       <c r="AG5" t="n">
-        <v>47.3598986485402</v>
+        <v>61.17752855420036</v>
       </c>
       <c r="AH5" t="n">
-        <v>214.5</v>
+        <v>345.6</v>
       </c>
       <c r="AI5" t="n">
-        <v>50.74297981001904</v>
+        <v>58.04515483655805</v>
       </c>
       <c r="AJ5" t="n">
-        <v>204.2</v>
+        <v>294.8</v>
       </c>
       <c r="AK5" t="n">
-        <v>29.80201335480541</v>
+        <v>19.5540277180943</v>
       </c>
       <c r="AL5" t="n">
-        <v>227.3</v>
+        <v>310</v>
       </c>
       <c r="AM5" t="n">
-        <v>35.04582714104491</v>
+        <v>41.66053288185354</v>
       </c>
       <c r="AN5" t="n">
-        <v>227.3</v>
+        <v>336.3</v>
       </c>
       <c r="AO5" t="n">
-        <v>44.73935627610214</v>
+        <v>34.42106912924118</v>
       </c>
       <c r="AP5" t="n">
-        <v>207.6</v>
+        <v>315.9</v>
       </c>
       <c r="AQ5" t="n">
-        <v>30.39473638642059</v>
+        <v>43.72973816523488</v>
       </c>
       <c r="AR5" t="n">
-        <v>209.7</v>
+        <v>331.4</v>
       </c>
       <c r="AS5" t="n">
-        <v>37.21572248391801</v>
+        <v>35.49704213029587</v>
       </c>
       <c r="AT5" t="n">
-        <v>214.6</v>
+        <v>319.4</v>
       </c>
       <c r="AU5" t="n">
-        <v>49.02285181423048</v>
+        <v>39.7421690399505</v>
       </c>
       <c r="AV5" t="n">
-        <v>215.2</v>
+        <v>318.5</v>
       </c>
       <c r="AW5" t="n">
-        <v>52.02460956124515</v>
+        <v>28.61904959987316</v>
       </c>
       <c r="AX5" t="n">
-        <v>248.1</v>
+        <v>307.8</v>
       </c>
       <c r="AY5" t="n">
-        <v>70.66180014689691</v>
+        <v>21.57220433799013</v>
       </c>
       <c r="AZ5" t="n">
-        <v>234</v>
+        <v>323.3</v>
       </c>
       <c r="BA5" t="n">
-        <v>30.77986354745583</v>
+        <v>37.09730448428834</v>
       </c>
       <c r="BB5" t="n">
-        <v>238.8</v>
+        <v>338.3</v>
       </c>
       <c r="BC5" t="n">
-        <v>42.98325255259309</v>
+        <v>57.53094819312471</v>
       </c>
       <c r="BD5" t="n">
-        <v>269.6</v>
+        <v>367.1</v>
       </c>
       <c r="BE5" t="n">
-        <v>43.14904402185523</v>
+        <v>84.44933392277289</v>
       </c>
       <c r="BF5" t="n">
-        <v>240.9</v>
+        <v>346.7</v>
       </c>
       <c r="BG5" t="n">
-        <v>49.000918358741</v>
+        <v>41.39335695495112</v>
       </c>
       <c r="BH5" t="n">
-        <v>257.2</v>
+        <v>341.5</v>
       </c>
       <c r="BI5" t="n">
-        <v>83.08646099094605</v>
+        <v>49.62912451373689</v>
       </c>
       <c r="BJ5" t="n">
-        <v>6424.900000000001</v>
+        <v>9713.700000000001</v>
       </c>
       <c r="BK5" t="n">
-        <v>214.1633333333334</v>
+        <v>323.79</v>
       </c>
     </row>
     <row r="6">
@@ -1514,190 +1514,190 @@
         <v>5</v>
       </c>
       <c r="B6" t="n">
-        <v>174.8</v>
+        <v>302.6</v>
       </c>
       <c r="C6" t="n">
-        <v>13.91977011304425</v>
+        <v>31.72128622865094</v>
       </c>
       <c r="D6" t="n">
-        <v>186.5</v>
+        <v>295.7</v>
       </c>
       <c r="E6" t="n">
-        <v>15.76229678695335</v>
+        <v>35.62878050116226</v>
       </c>
       <c r="F6" t="n">
-        <v>195.1</v>
+        <v>297.6</v>
       </c>
       <c r="G6" t="n">
-        <v>26.04784060147788</v>
+        <v>34.50854966526412</v>
       </c>
       <c r="H6" t="n">
-        <v>201.9</v>
+        <v>291.6</v>
       </c>
       <c r="I6" t="n">
-        <v>31.79135102508228</v>
+        <v>36.73744683561992</v>
       </c>
       <c r="J6" t="n">
-        <v>183</v>
+        <v>276.2</v>
       </c>
       <c r="K6" t="n">
-        <v>34.77930419085465</v>
+        <v>29.1128837458607</v>
       </c>
       <c r="L6" t="n">
-        <v>213.8</v>
+        <v>290.5</v>
       </c>
       <c r="M6" t="n">
-        <v>51.35328616554154</v>
+        <v>33.56262802582658</v>
       </c>
       <c r="N6" t="n">
-        <v>189.8</v>
+        <v>300.9</v>
       </c>
       <c r="O6" t="n">
-        <v>53.41310700567792</v>
+        <v>48.03009473236546</v>
       </c>
       <c r="P6" t="n">
-        <v>212.3</v>
+        <v>313.7</v>
       </c>
       <c r="Q6" t="n">
-        <v>39.83478379507036</v>
+        <v>34.78807266866045</v>
       </c>
       <c r="R6" t="n">
-        <v>222.3</v>
+        <v>317.7</v>
       </c>
       <c r="S6" t="n">
-        <v>40.78492368510698</v>
+        <v>31.43580760852184</v>
       </c>
       <c r="T6" t="n">
-        <v>247.8</v>
+        <v>333</v>
       </c>
       <c r="U6" t="n">
-        <v>79.2777396246891</v>
+        <v>60.24450182381791</v>
       </c>
       <c r="V6" t="n">
-        <v>233.1</v>
+        <v>343.6</v>
       </c>
       <c r="W6" t="n">
-        <v>49.02744129566625</v>
+        <v>55.41516038053124</v>
       </c>
       <c r="X6" t="n">
-        <v>191.9</v>
+        <v>348.3</v>
       </c>
       <c r="Y6" t="n">
-        <v>43.18437217327583</v>
+        <v>53.6359021551796</v>
       </c>
       <c r="Z6" t="n">
-        <v>181.7</v>
+        <v>345.3</v>
       </c>
       <c r="AA6" t="n">
-        <v>45.01566394045522</v>
+        <v>58.98143775799297</v>
       </c>
       <c r="AB6" t="n">
-        <v>203.1</v>
+        <v>340.1</v>
       </c>
       <c r="AC6" t="n">
-        <v>26.74116676586869</v>
+        <v>51.16727469779878</v>
       </c>
       <c r="AD6" t="n">
-        <v>199.9</v>
+        <v>350.2</v>
       </c>
       <c r="AE6" t="n">
-        <v>28.94978410973042</v>
+        <v>72.40966786279303</v>
       </c>
       <c r="AF6" t="n">
-        <v>206.4</v>
+        <v>344.3</v>
       </c>
       <c r="AG6" t="n">
-        <v>27.13742802846283</v>
+        <v>78.48318291200988</v>
       </c>
       <c r="AH6" t="n">
-        <v>203.7</v>
+        <v>372.4</v>
       </c>
       <c r="AI6" t="n">
-        <v>34.82542174906142</v>
+        <v>63.03364181133754</v>
       </c>
       <c r="AJ6" t="n">
-        <v>209.8</v>
+        <v>324.7</v>
       </c>
       <c r="AK6" t="n">
-        <v>54.18634514340306</v>
+        <v>60.22798352925324</v>
       </c>
       <c r="AL6" t="n">
-        <v>224.3</v>
+        <v>368</v>
       </c>
       <c r="AM6" t="n">
-        <v>58.50307684216275</v>
+        <v>78.92908209272423</v>
       </c>
       <c r="AN6" t="n">
-        <v>212.5</v>
+        <v>343.1</v>
       </c>
       <c r="AO6" t="n">
-        <v>33.15493930020081</v>
+        <v>46.15506472750309</v>
       </c>
       <c r="AP6" t="n">
-        <v>197.1</v>
+        <v>311.3</v>
       </c>
       <c r="AQ6" t="n">
-        <v>43.31616326499844</v>
+        <v>29.81962441078023</v>
       </c>
       <c r="AR6" t="n">
-        <v>193</v>
+        <v>332</v>
       </c>
       <c r="AS6" t="n">
-        <v>40.80931266267542</v>
+        <v>26.95922847560738</v>
       </c>
       <c r="AT6" t="n">
-        <v>209.1</v>
+        <v>345.7</v>
       </c>
       <c r="AU6" t="n">
-        <v>57.66532753743795</v>
+        <v>68.43544403304475</v>
       </c>
       <c r="AV6" t="n">
-        <v>200.6</v>
+        <v>308</v>
       </c>
       <c r="AW6" t="n">
-        <v>56.22668405659363</v>
+        <v>19.02104098097683</v>
       </c>
       <c r="AX6" t="n">
-        <v>229.2</v>
+        <v>319.3</v>
       </c>
       <c r="AY6" t="n">
-        <v>46.59356178701088</v>
+        <v>34.86559909136798</v>
       </c>
       <c r="AZ6" t="n">
-        <v>217.3</v>
+        <v>336</v>
       </c>
       <c r="BA6" t="n">
-        <v>60.19144457478987</v>
+        <v>43.02092514114498</v>
       </c>
       <c r="BB6" t="n">
-        <v>237</v>
+        <v>321.6</v>
       </c>
       <c r="BC6" t="n">
-        <v>101.6700545883595</v>
+        <v>22.72091547451378</v>
       </c>
       <c r="BD6" t="n">
-        <v>243.9</v>
+        <v>359.4</v>
       </c>
       <c r="BE6" t="n">
-        <v>51.23172845024848</v>
+        <v>67.42877723939534</v>
       </c>
       <c r="BF6" t="n">
-        <v>252.6</v>
+        <v>356.5</v>
       </c>
       <c r="BG6" t="n">
-        <v>51.44744891634569</v>
+        <v>59.4293698435378</v>
       </c>
       <c r="BH6" t="n">
-        <v>287.2</v>
+        <v>369.1</v>
       </c>
       <c r="BI6" t="n">
-        <v>50.1772856978135</v>
+        <v>105.9409741318249</v>
       </c>
       <c r="BJ6" t="n">
-        <v>6360.700000000001</v>
+        <v>9858.4</v>
       </c>
       <c r="BK6" t="n">
-        <v>212.0233333333334</v>
+        <v>328.6133333333333</v>
       </c>
     </row>
     <row r="7">
@@ -1705,190 +1705,190 @@
         <v>6</v>
       </c>
       <c r="B7" t="n">
-        <v>201.2</v>
+        <v>271.5</v>
       </c>
       <c r="C7" t="n">
-        <v>21.21697433660134</v>
+        <v>22.27217995616953</v>
       </c>
       <c r="D7" t="n">
-        <v>193.9</v>
+        <v>312.3</v>
       </c>
       <c r="E7" t="n">
-        <v>25.09760944791356</v>
+        <v>46.15853117247125</v>
       </c>
       <c r="F7" t="n">
-        <v>200.5</v>
+        <v>281</v>
       </c>
       <c r="G7" t="n">
-        <v>32.66879244783927</v>
+        <v>33.05147500490712</v>
       </c>
       <c r="H7" t="n">
-        <v>200.7</v>
+        <v>294.2</v>
       </c>
       <c r="I7" t="n">
-        <v>28.75082607508869</v>
+        <v>36.41098735272088</v>
       </c>
       <c r="J7" t="n">
-        <v>191.4</v>
+        <v>294.9</v>
       </c>
       <c r="K7" t="n">
-        <v>28.12187760445593</v>
+        <v>33.93950500522952</v>
       </c>
       <c r="L7" t="n">
-        <v>180.7</v>
+        <v>299.9</v>
       </c>
       <c r="M7" t="n">
-        <v>32.33280068289785</v>
+        <v>27.20827080135744</v>
       </c>
       <c r="N7" t="n">
-        <v>237.2</v>
+        <v>318</v>
       </c>
       <c r="O7" t="n">
-        <v>53.95145966514715</v>
+        <v>31.25379976898809</v>
       </c>
       <c r="P7" t="n">
-        <v>245.6</v>
+        <v>317.9</v>
       </c>
       <c r="Q7" t="n">
-        <v>105.837800430659</v>
+        <v>35.33963780233181</v>
       </c>
       <c r="R7" t="n">
-        <v>215.5</v>
+        <v>362.9</v>
       </c>
       <c r="S7" t="n">
-        <v>45.684242359921</v>
+        <v>71.29579230221094</v>
       </c>
       <c r="T7" t="n">
-        <v>220.3</v>
+        <v>350.2</v>
       </c>
       <c r="U7" t="n">
-        <v>38.14197163231078</v>
+        <v>57.79584760170924</v>
       </c>
       <c r="V7" t="n">
-        <v>211.8</v>
+        <v>355.5</v>
       </c>
       <c r="W7" t="n">
-        <v>68.44238452888678</v>
+        <v>48.02134941877415</v>
       </c>
       <c r="X7" t="n">
-        <v>206.7</v>
+        <v>335.1</v>
       </c>
       <c r="Y7" t="n">
-        <v>26.92972335543015</v>
+        <v>63.30947796341398</v>
       </c>
       <c r="Z7" t="n">
-        <v>217.7</v>
+        <v>310.1</v>
       </c>
       <c r="AA7" t="n">
-        <v>71.31065838989288</v>
+        <v>30.40213808270727</v>
       </c>
       <c r="AB7" t="n">
-        <v>235.3</v>
+        <v>345.5</v>
       </c>
       <c r="AC7" t="n">
-        <v>35.85261496739115</v>
+        <v>61.65427803486146</v>
       </c>
       <c r="AD7" t="n">
-        <v>211.4</v>
+        <v>370.5</v>
       </c>
       <c r="AE7" t="n">
-        <v>26.20763247605552</v>
+        <v>84.15254006861588</v>
       </c>
       <c r="AF7" t="n">
-        <v>187.4</v>
+        <v>294.7</v>
       </c>
       <c r="AG7" t="n">
-        <v>38.79226727068166</v>
+        <v>48.016767904556</v>
       </c>
       <c r="AH7" t="n">
-        <v>225.7</v>
+        <v>343.8</v>
       </c>
       <c r="AI7" t="n">
-        <v>78.65627756256967</v>
+        <v>81.11941814386984</v>
       </c>
       <c r="AJ7" t="n">
-        <v>230.1</v>
+        <v>357.6</v>
       </c>
       <c r="AK7" t="n">
-        <v>44.24353060052961</v>
+        <v>73.6847338327282</v>
       </c>
       <c r="AL7" t="n">
-        <v>275.7</v>
+        <v>338.8</v>
       </c>
       <c r="AM7" t="n">
-        <v>88.11588960000347</v>
+        <v>63.66286201546393</v>
       </c>
       <c r="AN7" t="n">
-        <v>212.5</v>
+        <v>316.8</v>
       </c>
       <c r="AO7" t="n">
-        <v>46.83214707868945</v>
+        <v>28.65937891860185</v>
       </c>
       <c r="AP7" t="n">
-        <v>215.1</v>
+        <v>307.4</v>
       </c>
       <c r="AQ7" t="n">
-        <v>46.94560682321617</v>
+        <v>17.66465397340123</v>
       </c>
       <c r="AR7" t="n">
-        <v>267.1</v>
+        <v>334.2</v>
       </c>
       <c r="AS7" t="n">
-        <v>87.82192209237964</v>
+        <v>61.40651431240826</v>
       </c>
       <c r="AT7" t="n">
-        <v>277.2</v>
+        <v>322.1</v>
       </c>
       <c r="AU7" t="n">
-        <v>83.60598064731973</v>
+        <v>29.88126503346202</v>
       </c>
       <c r="AV7" t="n">
-        <v>215</v>
+        <v>326.2</v>
       </c>
       <c r="AW7" t="n">
-        <v>47.51631298827804</v>
+        <v>48.31107533475114</v>
       </c>
       <c r="AX7" t="n">
-        <v>219.5</v>
+        <v>313.7</v>
       </c>
       <c r="AY7" t="n">
-        <v>52.34548691148073</v>
+        <v>30.27887052054617</v>
       </c>
       <c r="AZ7" t="n">
-        <v>232</v>
+        <v>328</v>
       </c>
       <c r="BA7" t="n">
-        <v>45.04442251822083</v>
+        <v>43.92265930018355</v>
       </c>
       <c r="BB7" t="n">
-        <v>249.8</v>
+        <v>322</v>
       </c>
       <c r="BC7" t="n">
-        <v>43.16665379665188</v>
+        <v>64.60340548299293</v>
       </c>
       <c r="BD7" t="n">
-        <v>237.1</v>
+        <v>319.9</v>
       </c>
       <c r="BE7" t="n">
-        <v>43.37384004212678</v>
+        <v>22.65590430770752</v>
       </c>
       <c r="BF7" t="n">
-        <v>255.4</v>
+        <v>348.5</v>
       </c>
       <c r="BG7" t="n">
-        <v>92.93352462916705</v>
+        <v>65.81679117064277</v>
       </c>
       <c r="BH7" t="n">
-        <v>274.6</v>
+        <v>305.8</v>
       </c>
       <c r="BI7" t="n">
-        <v>98.59533457522217</v>
+        <v>67.47710722904472</v>
       </c>
       <c r="BJ7" t="n">
-        <v>6744.1</v>
+        <v>9698.999999999998</v>
       </c>
       <c r="BK7" t="n">
-        <v>224.8033333333333</v>
+        <v>323.3</v>
       </c>
     </row>
     <row r="8">
@@ -1896,190 +1896,190 @@
         <v>7</v>
       </c>
       <c r="B8" t="n">
-        <v>186.1</v>
+        <v>285</v>
       </c>
       <c r="C8" t="n">
-        <v>24.49265195931221</v>
+        <v>40.18706259482024</v>
       </c>
       <c r="D8" t="n">
-        <v>186.8</v>
+        <v>290.1</v>
       </c>
       <c r="E8" t="n">
-        <v>23.17239737273638</v>
+        <v>38.52648439710013</v>
       </c>
       <c r="F8" t="n">
-        <v>209.2</v>
+        <v>282</v>
       </c>
       <c r="G8" t="n">
-        <v>64.10584996706618</v>
+        <v>33.83193757383695</v>
       </c>
       <c r="H8" t="n">
-        <v>221.9</v>
+        <v>283.7</v>
       </c>
       <c r="I8" t="n">
-        <v>25.66105999369473</v>
+        <v>31.74917321758159</v>
       </c>
       <c r="J8" t="n">
-        <v>197.5</v>
+        <v>289.1</v>
       </c>
       <c r="K8" t="n">
-        <v>36.78382796827975</v>
+        <v>33.62276014844706</v>
       </c>
       <c r="L8" t="n">
-        <v>222.4</v>
+        <v>287.4</v>
       </c>
       <c r="M8" t="n">
-        <v>55.25251125514568</v>
+        <v>32.89133624527894</v>
       </c>
       <c r="N8" t="n">
-        <v>202.7</v>
+        <v>298.5</v>
       </c>
       <c r="O8" t="n">
-        <v>40.57351352791622</v>
+        <v>41.23893791066885</v>
       </c>
       <c r="P8" t="n">
-        <v>183.9</v>
+        <v>305.5</v>
       </c>
       <c r="Q8" t="n">
-        <v>35.08119154190747</v>
+        <v>34.61863659938098</v>
       </c>
       <c r="R8" t="n">
-        <v>211.9</v>
+        <v>336</v>
       </c>
       <c r="S8" t="n">
-        <v>40.15333111959704</v>
+        <v>18.08314132002512</v>
       </c>
       <c r="T8" t="n">
-        <v>207.1</v>
+        <v>344.9</v>
       </c>
       <c r="U8" t="n">
-        <v>48.44471075360033</v>
+        <v>78.98917647374226</v>
       </c>
       <c r="V8" t="n">
-        <v>198.3</v>
+        <v>361.2</v>
       </c>
       <c r="W8" t="n">
-        <v>29.24055403031892</v>
+        <v>76.82551659442323</v>
       </c>
       <c r="X8" t="n">
-        <v>220.6</v>
+        <v>344.6</v>
       </c>
       <c r="Y8" t="n">
-        <v>39.69685126052191</v>
+        <v>55.17644424933524</v>
       </c>
       <c r="Z8" t="n">
-        <v>185.1</v>
+        <v>316.8</v>
       </c>
       <c r="AA8" t="n">
-        <v>36.65910528095305</v>
+        <v>34.92792579011815</v>
       </c>
       <c r="AB8" t="n">
-        <v>225.8</v>
+        <v>323.6</v>
       </c>
       <c r="AC8" t="n">
-        <v>31.26595592653453</v>
+        <v>24.63412267567083</v>
       </c>
       <c r="AD8" t="n">
-        <v>196.7</v>
+        <v>357.8</v>
       </c>
       <c r="AE8" t="n">
-        <v>51.89229229856781</v>
+        <v>85.54039981201865</v>
       </c>
       <c r="AF8" t="n">
-        <v>230.8</v>
+        <v>312.4</v>
       </c>
       <c r="AG8" t="n">
-        <v>31.05736627597389</v>
+        <v>33.79704129062188</v>
       </c>
       <c r="AH8" t="n">
-        <v>209</v>
+        <v>337.4</v>
       </c>
       <c r="AI8" t="n">
-        <v>41.80669802794763</v>
+        <v>81.23078234265628</v>
       </c>
       <c r="AJ8" t="n">
-        <v>214.7</v>
+        <v>323.7</v>
       </c>
       <c r="AK8" t="n">
-        <v>83.5991028659997</v>
+        <v>64.60967419821895</v>
       </c>
       <c r="AL8" t="n">
-        <v>206.6</v>
+        <v>342.6</v>
       </c>
       <c r="AM8" t="n">
-        <v>41.02243288738492</v>
+        <v>68.34208074093149</v>
       </c>
       <c r="AN8" t="n">
-        <v>190.3</v>
+        <v>319.2</v>
       </c>
       <c r="AO8" t="n">
-        <v>41.52842400091773</v>
+        <v>17.20929981143916</v>
       </c>
       <c r="AP8" t="n">
-        <v>272.8</v>
+        <v>341.9</v>
       </c>
       <c r="AQ8" t="n">
-        <v>82.22262462363993</v>
+        <v>71.65396011386949</v>
       </c>
       <c r="AR8" t="n">
-        <v>206.7</v>
+        <v>338.6</v>
       </c>
       <c r="AS8" t="n">
-        <v>42.10712528777048</v>
+        <v>52.83975775871801</v>
       </c>
       <c r="AT8" t="n">
-        <v>214.8</v>
+        <v>334.6</v>
       </c>
       <c r="AU8" t="n">
-        <v>42.64926728561699</v>
+        <v>49.67735902803208</v>
       </c>
       <c r="AV8" t="n">
-        <v>211.1</v>
+        <v>319.8</v>
       </c>
       <c r="AW8" t="n">
-        <v>63.16557606798184</v>
+        <v>24.04079865561874</v>
       </c>
       <c r="AX8" t="n">
-        <v>227.3</v>
+        <v>339.6</v>
       </c>
       <c r="AY8" t="n">
-        <v>50.05606856316225</v>
+        <v>57.29781845759923</v>
       </c>
       <c r="AZ8" t="n">
-        <v>233.5</v>
+        <v>328</v>
       </c>
       <c r="BA8" t="n">
-        <v>72.30387264870396</v>
+        <v>30.81233519225701</v>
       </c>
       <c r="BB8" t="n">
-        <v>220.6</v>
+        <v>320.7</v>
       </c>
       <c r="BC8" t="n">
-        <v>64.69497662106387</v>
+        <v>10.61178590059185</v>
       </c>
       <c r="BD8" t="n">
-        <v>225.8</v>
+        <v>340.1</v>
       </c>
       <c r="BE8" t="n">
-        <v>61.88182285615058</v>
+        <v>34.7</v>
       </c>
       <c r="BF8" t="n">
-        <v>218.8</v>
+        <v>362.1</v>
       </c>
       <c r="BG8" t="n">
-        <v>67.59112367759542</v>
+        <v>80.8955499394126</v>
       </c>
       <c r="BH8" t="n">
-        <v>267.2</v>
+        <v>344.5</v>
       </c>
       <c r="BI8" t="n">
-        <v>72.55866591937864</v>
+        <v>65.5839157110949</v>
       </c>
       <c r="BJ8" t="n">
-        <v>6406.000000000001</v>
+        <v>9711.400000000001</v>
       </c>
       <c r="BK8" t="n">
-        <v>213.5333333333334</v>
+        <v>323.7133333333334</v>
       </c>
     </row>
     <row r="9">
@@ -2087,190 +2087,190 @@
         <v>8</v>
       </c>
       <c r="B9" t="n">
-        <v>189.2</v>
+        <v>294</v>
       </c>
       <c r="C9" t="n">
-        <v>17.808986495587</v>
+        <v>33.31666249791537</v>
       </c>
       <c r="D9" t="n">
-        <v>203.7</v>
+        <v>290</v>
       </c>
       <c r="E9" t="n">
-        <v>16.63760800115209</v>
+        <v>31.49920633920798</v>
       </c>
       <c r="F9" t="n">
-        <v>211.2</v>
+        <v>290.5</v>
       </c>
       <c r="G9" t="n">
-        <v>20.0539272961682</v>
+        <v>35.35604615903764</v>
       </c>
       <c r="H9" t="n">
-        <v>212.3</v>
+        <v>279.9</v>
       </c>
       <c r="I9" t="n">
-        <v>38.89485827201328</v>
+        <v>26.11685279661391</v>
       </c>
       <c r="J9" t="n">
-        <v>195</v>
+        <v>297.4</v>
       </c>
       <c r="K9" t="n">
-        <v>42.5440947723653</v>
+        <v>31.73704460090763</v>
       </c>
       <c r="L9" t="n">
-        <v>203.1</v>
+        <v>306</v>
       </c>
       <c r="M9" t="n">
-        <v>33.44981315343929</v>
+        <v>36.95131932691984</v>
       </c>
       <c r="N9" t="n">
-        <v>181.6</v>
+        <v>294.8</v>
       </c>
       <c r="O9" t="n">
-        <v>58.37328155928875</v>
+        <v>27.38539756877742</v>
       </c>
       <c r="P9" t="n">
-        <v>259.5</v>
+        <v>296.2</v>
       </c>
       <c r="Q9" t="n">
-        <v>77.32690346832725</v>
+        <v>32.31965346348874</v>
       </c>
       <c r="R9" t="n">
-        <v>182.7</v>
+        <v>323.4</v>
       </c>
       <c r="S9" t="n">
-        <v>42.07148678142953</v>
+        <v>27.42699400225989</v>
       </c>
       <c r="T9" t="n">
-        <v>197.8</v>
+        <v>325.2</v>
       </c>
       <c r="U9" t="n">
-        <v>28.65588944702293</v>
+        <v>33.16262957004465</v>
       </c>
       <c r="V9" t="n">
-        <v>202.5</v>
+        <v>329.3</v>
       </c>
       <c r="W9" t="n">
-        <v>43.83890965797393</v>
+        <v>59.45763197437315</v>
       </c>
       <c r="X9" t="n">
-        <v>203.8</v>
+        <v>319.1</v>
       </c>
       <c r="Y9" t="n">
-        <v>36.86678722102049</v>
+        <v>32.02327278714654</v>
       </c>
       <c r="Z9" t="n">
-        <v>198.3</v>
+        <v>335.8</v>
       </c>
       <c r="AA9" t="n">
-        <v>38.19960732782472</v>
+        <v>14.22532952166662</v>
       </c>
       <c r="AB9" t="n">
-        <v>219.2</v>
+        <v>356.1</v>
       </c>
       <c r="AC9" t="n">
-        <v>27.87400222429495</v>
+        <v>61.66433328918752</v>
       </c>
       <c r="AD9" t="n">
-        <v>198.8</v>
+        <v>324.7</v>
       </c>
       <c r="AE9" t="n">
-        <v>54.18819059536865</v>
+        <v>61.31402775874375</v>
       </c>
       <c r="AF9" t="n">
-        <v>185.3</v>
+        <v>348.8</v>
       </c>
       <c r="AG9" t="n">
-        <v>40.97816491742889</v>
+        <v>82.32350818569384</v>
       </c>
       <c r="AH9" t="n">
-        <v>215.2</v>
+        <v>355</v>
       </c>
       <c r="AI9" t="n">
-        <v>14.44160655882856</v>
+        <v>81.93900170248598</v>
       </c>
       <c r="AJ9" t="n">
-        <v>210.8</v>
+        <v>307.7</v>
       </c>
       <c r="AK9" t="n">
-        <v>42.62815970693551</v>
+        <v>35.50225344960513</v>
       </c>
       <c r="AL9" t="n">
-        <v>213.4</v>
+        <v>341.3</v>
       </c>
       <c r="AM9" t="n">
-        <v>38.30456891808078</v>
+        <v>61.25528548623376</v>
       </c>
       <c r="AN9" t="n">
-        <v>194.3</v>
+        <v>339</v>
       </c>
       <c r="AO9" t="n">
-        <v>64.82599787122447</v>
+        <v>36.98378022863536</v>
       </c>
       <c r="AP9" t="n">
-        <v>227</v>
+        <v>316.7</v>
       </c>
       <c r="AQ9" t="n">
-        <v>25.94224354214569</v>
+        <v>20.2881738951538</v>
       </c>
       <c r="AR9" t="n">
-        <v>232.1</v>
+        <v>314.4</v>
       </c>
       <c r="AS9" t="n">
-        <v>70.4818416331469</v>
+        <v>26.77013261080341</v>
       </c>
       <c r="AT9" t="n">
-        <v>221.2</v>
+        <v>337.3</v>
       </c>
       <c r="AU9" t="n">
-        <v>41.15531557405435</v>
+        <v>54.29742166990989</v>
       </c>
       <c r="AV9" t="n">
-        <v>224.2</v>
+        <v>344.5</v>
       </c>
       <c r="AW9" t="n">
-        <v>65.96938683965465</v>
+        <v>59.29460346439632</v>
       </c>
       <c r="AX9" t="n">
-        <v>224.7</v>
+        <v>323.5</v>
       </c>
       <c r="AY9" t="n">
-        <v>47.32451795845363</v>
+        <v>63.60227983335189</v>
       </c>
       <c r="AZ9" t="n">
-        <v>234.4</v>
+        <v>329</v>
       </c>
       <c r="BA9" t="n">
-        <v>59.50495777664244</v>
+        <v>57.5273847832491</v>
       </c>
       <c r="BB9" t="n">
-        <v>219.2</v>
+        <v>335.7</v>
       </c>
       <c r="BC9" t="n">
-        <v>57.45572208231309</v>
+        <v>39.29134764805097</v>
       </c>
       <c r="BD9" t="n">
-        <v>224.3</v>
+        <v>315.3</v>
       </c>
       <c r="BE9" t="n">
-        <v>80.58293864088105</v>
+        <v>61.509430171316</v>
       </c>
       <c r="BF9" t="n">
-        <v>292.9</v>
+        <v>371.7</v>
       </c>
       <c r="BG9" t="n">
-        <v>97.50635876700555</v>
+        <v>87.9079632342827</v>
       </c>
       <c r="BH9" t="n">
-        <v>245</v>
+        <v>347.4</v>
       </c>
       <c r="BI9" t="n">
-        <v>102.4890238025517</v>
+        <v>73.70237445293063</v>
       </c>
       <c r="BJ9" t="n">
-        <v>6422.7</v>
+        <v>9689.700000000001</v>
       </c>
       <c r="BK9" t="n">
-        <v>214.09</v>
+        <v>322.99</v>
       </c>
     </row>
     <row r="10">
@@ -2278,190 +2278,190 @@
         <v>9</v>
       </c>
       <c r="B10" t="n">
-        <v>193.8</v>
+        <v>333.1</v>
       </c>
       <c r="C10" t="n">
-        <v>22.95125268912353</v>
+        <v>31.19118465207758</v>
       </c>
       <c r="D10" t="n">
-        <v>198.3</v>
+        <v>285.1</v>
       </c>
       <c r="E10" t="n">
-        <v>20.83290666229751</v>
+        <v>36.40727949188184</v>
       </c>
       <c r="F10" t="n">
-        <v>217.3</v>
+        <v>288.6</v>
       </c>
       <c r="G10" t="n">
-        <v>50.84299361760674</v>
+        <v>32.64414189406731</v>
       </c>
       <c r="H10" t="n">
-        <v>199.5</v>
+        <v>273.7</v>
       </c>
       <c r="I10" t="n">
-        <v>35.19445979127965</v>
+        <v>25.89613870830939</v>
       </c>
       <c r="J10" t="n">
-        <v>195.6</v>
+        <v>296</v>
       </c>
       <c r="K10" t="n">
-        <v>30.60457482142171</v>
+        <v>31.35602015562562</v>
       </c>
       <c r="L10" t="n">
-        <v>197.6</v>
+        <v>304.5</v>
       </c>
       <c r="M10" t="n">
-        <v>20.85761251917391</v>
+        <v>35.51126581804709</v>
       </c>
       <c r="N10" t="n">
-        <v>218.1</v>
+        <v>305</v>
       </c>
       <c r="O10" t="n">
-        <v>76.81725066676104</v>
+        <v>36.08600836889556</v>
       </c>
       <c r="P10" t="n">
-        <v>189.5</v>
+        <v>304.9</v>
       </c>
       <c r="Q10" t="n">
-        <v>53.83725475913496</v>
+        <v>27.97302271832631</v>
       </c>
       <c r="R10" t="n">
-        <v>224.8</v>
+        <v>330.1</v>
       </c>
       <c r="S10" t="n">
-        <v>50.88968461289576</v>
+        <v>28.84943673626922</v>
       </c>
       <c r="T10" t="n">
-        <v>181.9</v>
+        <v>317.2</v>
       </c>
       <c r="U10" t="n">
-        <v>31.64316671889841</v>
+        <v>29.58310328549052</v>
       </c>
       <c r="V10" t="n">
-        <v>202.6</v>
+        <v>346.6</v>
       </c>
       <c r="W10" t="n">
-        <v>21.78164364780583</v>
+        <v>50.9670481782102</v>
       </c>
       <c r="X10" t="n">
-        <v>196.1</v>
+        <v>350.3</v>
       </c>
       <c r="Y10" t="n">
-        <v>16.80743882928033</v>
+        <v>52.07120125366804</v>
       </c>
       <c r="Z10" t="n">
-        <v>227.3</v>
+        <v>322.9</v>
       </c>
       <c r="AA10" t="n">
-        <v>65.67198794006467</v>
+        <v>26.53469426995533</v>
       </c>
       <c r="AB10" t="n">
-        <v>207.2</v>
+        <v>340.8</v>
       </c>
       <c r="AC10" t="n">
-        <v>43.09013808286068</v>
+        <v>62.98698278215904</v>
       </c>
       <c r="AD10" t="n">
-        <v>208.8</v>
+        <v>371.5</v>
       </c>
       <c r="AE10" t="n">
-        <v>26.47942597565136</v>
+        <v>82.72393849424724</v>
       </c>
       <c r="AF10" t="n">
-        <v>220.4</v>
+        <v>315.5</v>
       </c>
       <c r="AG10" t="n">
-        <v>34.33715189120961</v>
+        <v>62.98928480305202</v>
       </c>
       <c r="AH10" t="n">
-        <v>221</v>
+        <v>330.3</v>
       </c>
       <c r="AI10" t="n">
-        <v>37.69084769542866</v>
+        <v>56.14988869089591</v>
       </c>
       <c r="AJ10" t="n">
-        <v>191.6</v>
+        <v>353.4</v>
       </c>
       <c r="AK10" t="n">
-        <v>32.75728926513914</v>
+        <v>75.290371230324</v>
       </c>
       <c r="AL10" t="n">
-        <v>200.5</v>
+        <v>328</v>
       </c>
       <c r="AM10" t="n">
-        <v>30.74491827928642</v>
+        <v>61.69278726074872</v>
       </c>
       <c r="AN10" t="n">
-        <v>191.4</v>
+        <v>313.9</v>
       </c>
       <c r="AO10" t="n">
-        <v>42.88402966140193</v>
+        <v>15.32612149240636</v>
       </c>
       <c r="AP10" t="n">
-        <v>235.4</v>
+        <v>323.6</v>
       </c>
       <c r="AQ10" t="n">
-        <v>55.44763295218291</v>
+        <v>70.63596817486118</v>
       </c>
       <c r="AR10" t="n">
-        <v>205.2</v>
+        <v>341.2</v>
       </c>
       <c r="AS10" t="n">
-        <v>58.71762937994006</v>
+        <v>66.14952758712643</v>
       </c>
       <c r="AT10" t="n">
-        <v>189.4</v>
+        <v>319.7</v>
       </c>
       <c r="AU10" t="n">
-        <v>39.61363401658576</v>
+        <v>25.26281852842236</v>
       </c>
       <c r="AV10" t="n">
-        <v>233.1</v>
+        <v>356.8</v>
       </c>
       <c r="AW10" t="n">
-        <v>50.35960682928333</v>
+        <v>83.46112867676784</v>
       </c>
       <c r="AX10" t="n">
-        <v>193.2</v>
+        <v>355.2</v>
       </c>
       <c r="AY10" t="n">
-        <v>40.97023309672524</v>
+        <v>63.22784196855054</v>
       </c>
       <c r="AZ10" t="n">
-        <v>241.3</v>
+        <v>352.7</v>
       </c>
       <c r="BA10" t="n">
-        <v>35.8581929271401</v>
+        <v>53.11882905335922</v>
       </c>
       <c r="BB10" t="n">
-        <v>235.5</v>
+        <v>328.5</v>
       </c>
       <c r="BC10" t="n">
-        <v>60.51652666834077</v>
+        <v>60.6798978245679</v>
       </c>
       <c r="BD10" t="n">
-        <v>242.8</v>
+        <v>325.4</v>
       </c>
       <c r="BE10" t="n">
-        <v>41.66245312028565</v>
+        <v>33.9799941141843</v>
       </c>
       <c r="BF10" t="n">
-        <v>283</v>
+        <v>387.9</v>
       </c>
       <c r="BG10" t="n">
-        <v>119.58177118608</v>
+        <v>65.64061242858722</v>
       </c>
       <c r="BH10" t="n">
-        <v>343.7</v>
+        <v>331.6</v>
       </c>
       <c r="BI10" t="n">
-        <v>137.3725227256164</v>
+        <v>26.00846016203189</v>
       </c>
       <c r="BJ10" t="n">
-        <v>6485.9</v>
+        <v>9834</v>
       </c>
       <c r="BK10" t="n">
-        <v>216.1966666666667</v>
+        <v>327.8</v>
       </c>
     </row>
     <row r="11">
@@ -2469,190 +2469,190 @@
         <v>10</v>
       </c>
       <c r="B11" t="n">
-        <v>194.4</v>
+        <v>292.2</v>
       </c>
       <c r="C11" t="n">
-        <v>13.46254062203713</v>
+        <v>37.6</v>
       </c>
       <c r="D11" t="n">
-        <v>184.8</v>
+        <v>307</v>
       </c>
       <c r="E11" t="n">
-        <v>23.4085454481905</v>
+        <v>37.820629291433</v>
       </c>
       <c r="F11" t="n">
-        <v>190</v>
+        <v>282.4</v>
       </c>
       <c r="G11" t="n">
-        <v>15.44020725249503</v>
+        <v>33.04602850570701</v>
       </c>
       <c r="H11" t="n">
-        <v>191.4</v>
+        <v>307.9</v>
       </c>
       <c r="I11" t="n">
-        <v>39.6943320891031</v>
+        <v>30.46128690649822</v>
       </c>
       <c r="J11" t="n">
-        <v>201</v>
+        <v>299.7</v>
       </c>
       <c r="K11" t="n">
-        <v>40.31376935986016</v>
+        <v>30.74426775839684</v>
       </c>
       <c r="L11" t="n">
-        <v>200.3</v>
+        <v>324.2</v>
       </c>
       <c r="M11" t="n">
-        <v>44.71923523496349</v>
+        <v>23.37434491060658</v>
       </c>
       <c r="N11" t="n">
-        <v>208.5</v>
+        <v>290.4</v>
       </c>
       <c r="O11" t="n">
-        <v>42.86082127071295</v>
+        <v>33.47894860953672</v>
       </c>
       <c r="P11" t="n">
-        <v>246.3</v>
+        <v>328</v>
       </c>
       <c r="Q11" t="n">
-        <v>60.97384685256458</v>
+        <v>70.87171509142416</v>
       </c>
       <c r="R11" t="n">
-        <v>193.6</v>
+        <v>328.3</v>
       </c>
       <c r="S11" t="n">
-        <v>44.47740999653644</v>
+        <v>23.90836673635403</v>
       </c>
       <c r="T11" t="n">
-        <v>215.4</v>
+        <v>321</v>
       </c>
       <c r="U11" t="n">
-        <v>54.51641954494077</v>
+        <v>64.04685784642366</v>
       </c>
       <c r="V11" t="n">
-        <v>200.3</v>
+        <v>306.6</v>
       </c>
       <c r="W11" t="n">
-        <v>53.91298544877662</v>
+        <v>31.72128622865094</v>
       </c>
       <c r="X11" t="n">
-        <v>189</v>
+        <v>338.4</v>
       </c>
       <c r="Y11" t="n">
-        <v>41.73248135445579</v>
+        <v>55.52873130191253</v>
       </c>
       <c r="Z11" t="n">
-        <v>227.8</v>
+        <v>329.8</v>
       </c>
       <c r="AA11" t="n">
-        <v>34.89641815430346</v>
+        <v>33.70993918712995</v>
       </c>
       <c r="AB11" t="n">
-        <v>203.8</v>
+        <v>372.8</v>
       </c>
       <c r="AC11" t="n">
-        <v>16.36948380371232</v>
+        <v>60.65113354258105</v>
       </c>
       <c r="AD11" t="n">
-        <v>190.9</v>
+        <v>319.6</v>
       </c>
       <c r="AE11" t="n">
-        <v>43.6404628756387</v>
+        <v>62.34292261355735</v>
       </c>
       <c r="AF11" t="n">
-        <v>214.1</v>
+        <v>325.3</v>
       </c>
       <c r="AG11" t="n">
-        <v>32.37112911221973</v>
+        <v>43.18344590233623</v>
       </c>
       <c r="AH11" t="n">
-        <v>213.4</v>
+        <v>317.4</v>
       </c>
       <c r="AI11" t="n">
-        <v>44.17510611192689</v>
+        <v>61.28490841961012</v>
       </c>
       <c r="AJ11" t="n">
-        <v>203.2</v>
+        <v>347</v>
       </c>
       <c r="AK11" t="n">
-        <v>33.00848375796743</v>
+        <v>81.60759768550965</v>
       </c>
       <c r="AL11" t="n">
-        <v>226.8</v>
+        <v>296.9</v>
       </c>
       <c r="AM11" t="n">
-        <v>53.13153489218997</v>
+        <v>25.1414001201206</v>
       </c>
       <c r="AN11" t="n">
-        <v>192.6</v>
+        <v>310.4</v>
       </c>
       <c r="AO11" t="n">
-        <v>42.10510657865623</v>
+        <v>32.65639294227089</v>
       </c>
       <c r="AP11" t="n">
-        <v>203.2</v>
+        <v>335.8</v>
       </c>
       <c r="AQ11" t="n">
-        <v>53.42621079582567</v>
+        <v>29.08882947112173</v>
       </c>
       <c r="AR11" t="n">
-        <v>213.2</v>
+        <v>311.7</v>
       </c>
       <c r="AS11" t="n">
-        <v>37.00216209899092</v>
+        <v>34.62961160625397</v>
       </c>
       <c r="AT11" t="n">
-        <v>228.2</v>
+        <v>316.4</v>
       </c>
       <c r="AU11" t="n">
-        <v>54.77006481646703</v>
+        <v>14.981321704042</v>
       </c>
       <c r="AV11" t="n">
-        <v>248.1</v>
+        <v>312.8</v>
       </c>
       <c r="AW11" t="n">
-        <v>56.07575233556835</v>
+        <v>13.42981757135964</v>
       </c>
       <c r="AX11" t="n">
-        <v>234.7</v>
+        <v>324.8</v>
       </c>
       <c r="AY11" t="n">
-        <v>63.74958823396431</v>
+        <v>30.45258609707885</v>
       </c>
       <c r="AZ11" t="n">
-        <v>233.9</v>
+        <v>314.2</v>
       </c>
       <c r="BA11" t="n">
-        <v>49.48019805942576</v>
+        <v>14.46927779814874</v>
       </c>
       <c r="BB11" t="n">
-        <v>211.3</v>
+        <v>330.4</v>
       </c>
       <c r="BC11" t="n">
-        <v>51.17430996115141</v>
+        <v>47.02169711952132</v>
       </c>
       <c r="BD11" t="n">
-        <v>264.1</v>
+        <v>344.7</v>
       </c>
       <c r="BE11" t="n">
-        <v>65.24178109156739</v>
+        <v>45.17532512334582</v>
       </c>
       <c r="BF11" t="n">
-        <v>254.1</v>
+        <v>318.5</v>
       </c>
       <c r="BG11" t="n">
-        <v>40.7</v>
+        <v>26.16199533674754</v>
       </c>
       <c r="BH11" t="n">
-        <v>278.6</v>
+        <v>312</v>
       </c>
       <c r="BI11" t="n">
-        <v>107.3631221602651</v>
+        <v>24.21982658897458</v>
       </c>
       <c r="BJ11" t="n">
-        <v>6457.000000000001</v>
+        <v>9566.6</v>
       </c>
       <c r="BK11" t="n">
-        <v>215.2333333333334</v>
+        <v>318.8866666666667</v>
       </c>
     </row>
   </sheetData>
